--- a/pensum/ok08/OK08_Nullpunktsanalyse_Oppgaver_v6.xlsx
+++ b/pensum/ok08/OK08_Nullpunktsanalyse_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="144">
   <si>
     <t xml:space="preserve">Nullpunktsanalyse: oppgaver til kapittel 8</t>
   </si>
@@ -65,10 +65,19 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Han har brukt dekningsbidraget i kroner der dekningsgraden i prosent skal stå</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Nordlys 2026: nullpunktet i kroner og i timer</t>
   </si>
   <si>
+    <t xml:space="preserve">Han har glemt å runde opp til hele timer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Han har glemt merverdiavgiften på salgsinntekten</t>
   </si>
   <si>
     <t xml:space="preserve">Situasjonen</t>
@@ -239,7 +248,16 @@
     <t xml:space="preserve">g) Tom sier at serviceavdelingen bærer seg fordi montørene har mye å gjøre. Svar ham i to setninger, med nullpunktet og resultatet ved 210 oppdrag.</t>
   </si>
   <si>
+    <t xml:space="preserve">Timeprisen opp 5 %</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Fire tiltak før et stille år: hva skjer med nullpunktet?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faste kostnader ned 10 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De gir samme nullpunkt</t>
   </si>
   <si>
     <t xml:space="preserve">Kari tror 2027 blir et stille år og vurderer fire tiltak: en ny servicebil på leasing og én til på kontoret, eller det motsatte: si opp leasingen på en bil og kutte kurs. Og timeprisen: opp 5 % for å tjene mer per time, eller ned 5 % for å vinne flere jobber. Hun endrer én ting om gangen, slik boka gjør det.</t>
@@ -634,7 +652,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -657,6 +675,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1115,7 +1137,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B1:Z33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1123,260 +1145,272 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>22</v>
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>22400000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>17216000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="13"/>
+      <c r="B14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>3840000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>14400</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
-        <v>30</v>
+      <c r="B21" s="15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="15" t="str">
+        <v>34</v>
+      </c>
+      <c r="C22" s="16" t="str">
         <f aca="false">IF(C14="","Skriv svaret i cellen C14.",IF(C14=(C12-C13),"Riktig.",IF(C14=(C12-C13-C15),"Du har trukket fra de faste kostnadene også. Det er driftsresultatet. Dekningsbidraget er salgsinntekt minus bare de variable.",IF(C14=(C12-C15),"Du har trukket fra de faste kostnadene. Det er de variable som skal trekkes fra.","Ikke riktig ennå. Dekningsbidrag = salgsinntekt − variable kostnader."))))</f>
         <v>Skriv svaret i cellen C14.</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="19" t="str">
+      <c r="B24" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G24" s="20" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(C12-C13)/C12)&lt;=0.0015,"Riktig.",IF(ABS(C24-C15/C12)&lt;=0.0015,"Du har delt de faste kostnadene på salgsinntekten. Dekningsgraden er dekningsbidraget delt på salgsinntekten.",IF(ABS(C24-(C12-C13)/(C13+C15))&lt;=0.0015,"Du har delt på kostnadene. Dekningsgraden er dekningsbidraget delt på salgsinntekten.",IF(ABS(C24-(C12-C13)/C12*100)&lt;=0.15,"Cellen er prosentformatert: skriv 23 % eller 0,23, ikke 23.","Ikke riktig ennå. Dekningsgrad = dekningsbidrag / salgsinntekt.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="19" t="str">
+      <c r="B25" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="20" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(ABS(C25-(C15/((C12-C13)/C12)))&lt;=50000,"Riktig.",IF(ABS(C25-(C15*100/(C12-C13)))&lt;=50000,"Du har delt på dekningsbidraget i kroner. Svaret ligner ikke en omsetning. I kroner deler du på dekningsgraden.",IF(ABS(C25-(C15/(((C12-C13)/C12)*100)))&lt;=50000,"Du har delt på dekningsgraden i prosent uten å gange med 100. Del på desimaltallet, eller gang med 100 først.",IF(ABS(C25-(C15*((C12-C13)/C12)))&lt;=50000,"Du har ganget med dekningsgraden. Nullpunktet er de faste kostnadene delt på dekningsgraden.","Ikke riktig ennå. Nullpunktomsetning = faste kostnader / dekningsgrad. Med dekningsgrad 23,1 % blir det om lag 16,6 millioner.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="19" t="str">
+      <c r="B26" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="20" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(ABS(C26-(ROUND((C12-C13)/C16,0)))&lt;=1,"Riktig.",IF(ABS(C26-(ROUND(C12/C16,0)))&lt;=1,"Du har delt salgsinntekten på timene. Det er omsetningen per time. Del dekningsbidraget på timene.",IF(ABS(C26-(ROUND(C15/C16,0)))&lt;=1,"Du har delt de faste kostnadene på timene. Det er de faste per time fra kapittel 2. Her er det dekningsbidraget som skal deles.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G27" s="19" t="str">
+      <c r="B27" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="20" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(ROUND(C15/((C12-C13)/C16),0)))&lt;=1,"Riktig.",IF(ABS(C27-(ROUND(C15/(C15/C16),0)))&lt;=1,"Du har delt på de faste kostnadene per time. Da får du bare timene tilbake. Del på dekningsbidraget per time, 360 kr.",IF(ABS(C27-(ROUND(C15/((C12-C13)/C12)/890,0)))&lt;=1,"Du har delt nullpunktomsetningen på timeprisen 890. Men omsetningen per time er 1 556 kr, for materiellet er med. Del de faste på dekningsbidraget per time.","Ikke riktig ennå. Nullpunkt i timer = faste kostnader / dekningsbidrag per time = 3 840 000 / 360."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="G29" s="19" t="str">
+      <c r="B29" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="G29" s="20" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Han har brukt dekningsbidraget i kroner der dekningsgraden i prosent skal stå","Riktig. I kroner deler du på dekningsgraden (23,1), ikke på dekningsbidraget (5 184 000). Se på størrelsen: et nullpunkt på 74 kr ligner ikke en omsetning. Kontroll: nullpunkt i timer × omsetning per time ≈ 16,6 millioner.","Ikke riktig. I kroner deler du på dekningsgraden (23,1), ikke på dekningsbidraget (5 184 000). Se på størrelsen: et nullpunkt på 74 kr ligner ikke en omsetning. Kontroll: nullpunkt i timer × omsetning per time ≈ 16,6 millioner."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="20"/>
+      <c r="B30" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22" t="str">
+      <c r="B31" s="23" t="str">
         <f aca="false">IF(C30="JA","Hint: a: 22 400 000 − 17 216 000 = 5 184 000. b: 5 184 000 / 22 400 000 = 23,1 %. c: 3 840 000 / 0,2314 = 16 592 593 kr. d: 5 184 000 / 14 400 = 360 kr. e: 3 840 000 / 360 = 10 667 timer.","")</f>
         <v/>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="B33" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1444,7 +1478,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Han har brukt dekningsbidraget i kroner der dekningsgraden i prosent skal stå,Han har glemt å runde opp til hele timer,Han har glemt merverdiavgiften på salgsinntekten"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
@@ -1479,7 +1513,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -1488,332 +1522,332 @@
       <c r="G2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>49</v>
+      <c r="B11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>22400000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="12" t="n">
+      <c r="B13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>16592593</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="12" t="n">
+      <c r="B14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>14400</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>10667</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>10667</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="12" t="n">
+      <c r="B18" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="13" t="n">
         <v>18500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="12" t="n">
+      <c r="B19" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="13" t="n">
         <v>11200</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="12" t="n">
+      <c r="B20" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="13" t="n">
         <v>2100000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="12" t="n">
+      <c r="B21" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="13" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="12" t="n">
+      <c r="B22" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="13" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" s="19" t="str">
+      <c r="B27" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="20" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(ABS(C27-(22400000-16592593))&lt;=50000,"Riktig.",IF(ABS(C27-(22400000-3840000))&lt;=50000,"Du har trukket fra de faste kostnadene. Trekk fra nullpunktomsetningen, 16 592 593.",IF(ABS(C27-(16592593-22400000))&lt;=50000,"Fortegnet er snudd. Salgsinntekten minus nullpunktomsetningen, så blir marginen positiv.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="19" t="str">
+      <c r="B28" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="20" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-((22400000-16592593)/22400000))&lt;=0.003,"Riktig.",IF(ABS(C28-((22400000-16592593)/16592593))&lt;=0.003,"Du har delt på nullpunktomsetningen. Marginen i prosent regnes av salgsinntekten, 22 400 000.","Ikke riktig ennå. Sikkerhetsmargin i prosent = sikkerhetsmargin i kroner / salgsinntekt. Cellen er prosentformatert.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G29" s="19" t="str">
+      <c r="B29" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="20" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(ABS(C29-(14400-10667))&lt;=1,"Riktig.",IF(ABS(C29-(10667))&lt;=1,"Det er nullpunktet. Marginen er timene over nullpunktet: 14 400 − 10 667.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="19" t="str">
+      <c r="B31" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="20" t="str">
         <f aca="false">IF(C31="","Skriv svaret i den gule cellen.",IF(C31=(18500-11200),"Riktig.",IF(ABS(C31-(18500))&lt;=0,"Det er prisen. Trekk fra de variable kostnadene på jobben, 11 200.",IF(ABS(C31-(11200))&lt;=0,"Det er de variable kostnadene. Dekningsbidraget er prisen minus dem.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G32" s="19" t="str">
+      <c r="B32" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="20" t="str">
         <f aca="false">IF(C32="","Skriv svaret i den gule cellen.",IF(C32=(288),"Riktig.",IF(ABS(C32-(287))&lt;=0,"287 oppdrag gir 287 × 7 300 = 2 095 100 kr, som ikke dekker de faste på 2 100 000. Rund opp til hele oppdrag.",IF(ABS(C32-(ROUND(2100000/18500,0)))&lt;=0,"Du har delt på prisen. Del på dekningsbidraget per oppdrag, 7 300.",IF(ABS(C32-(ROUND(2100000/11200,0)))&lt;=0,"Du har delt på de variable kostnadene. Del på dekningsbidraget per oppdrag.","Ikke riktig ennå. 2 100 000 / 7 300 = 287,7. Et halvt oppdrag finnes ikke, så rund opp til hele oppdrag.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" s="19" t="str">
+      <c r="B33" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G33" s="20" t="str">
         <f aca="false">IF(C33="","Skriv svaret i den gule cellen.",IF(C33=(210*7300-2100000),"Riktig.",IF(ABS(C33-(210*7300))&lt;=0,"Det er dekningsbidraget ved 210 oppdrag. Trekk fra de faste kostnadene, 2 100 000.",IF(ABS(C33-(210*18500-2100000))&lt;=0,"Du har brukt prisen. Bruk dekningsbidraget per oppdrag, 7 300.",IF(ABS(C33-(2100000-210*7300))&lt;=0,"Fortegnet er snudd: avdelingen taper penger, så resultatet er negativt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="B35" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="24" t="str">
+      <c r="B39" s="25" t="str">
         <f aca="false">IF(LEN(B36)&lt;40,"",IF(AND(ISNUMBER(SEARCH("288",B36)),ISNUMBER(SEARCH("567",B36))),"Bra: du bruker både nullpunktet 288 og tapet på 567 000. Si også at kapasiteten er 400, så det står ikke på montørene.",IF(OR(ISNUMBER(SEARCH("288",B36)),ISNUMBER(SEARCH("567",B36))),"Du har med ett av tallene. Ta med både nullpunktet (288 oppdrag) og resultatet ved 210 (−567 000 kr).","Tips: nullpunktet er 288 oppdrag, og 210 er 78 under. Ved 210 oppdrag taper avdelingen 567 000 kr. Mye å gjøre er ikke det samme som lønnsomt; kapasiteten er 400.")))</f>
         <v/>
       </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="20"/>
+      <c r="B40" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="22" t="str">
+      <c r="B41" s="23" t="str">
         <f aca="false">IF(C40="JA","Hint: a: 22 400 000 − 16 592 593 = 5 807 407. b: 5 807 407 / 22 400 000 = 25,9 %. c: 14 400 − 10 667 = 3 733. d: 18 500 − 11 200 = 7 300. e: 2 100 000 / 7 300 = 287,7 → 288. f: 210 × 7 300 − 2 100 000 = −567 000.","")</f>
         <v/>
       </c>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
+      <c r="B43" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1902,7 +1936,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G38"/>
+  <dimension ref="B1:Z38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1910,337 +1944,349 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>75</v>
+      <c r="B11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="12" t="n">
+      <c r="B12" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="13" t="n">
         <v>3840000</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <v>360</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="26" t="n">
+      <c r="B13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="27" t="n">
         <f aca="false">ROUND(C12*1.1,0)</f>
         <v>4224000</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <v>360</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="26" t="n">
+      <c r="B14" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="27" t="n">
         <f aca="false">ROUND(C12*0.9,0)</f>
         <v>3456000</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <v>360</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="12" t="n">
+      <c r="B15" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>3840000</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="28" t="n">
         <f aca="false">D12+890*0.05</f>
         <v>404.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>3840000</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="28" t="n">
         <f aca="false">D12-890*0.05</f>
         <v>315.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="B18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="19" t="str">
+      <c r="B21" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="20" t="str">
         <f aca="false">IF(C21="","Skriv svaret i den gule cellen.",IF(ABS(C21-(ROUND(3840000*1.1/360,0)))&lt;=1,"Riktig.",IF(ABS(C21-(ROUND(3840000/360,0)))&lt;=1,"Det er nullpunktet i dag. Bruk de nye faste kostnadene, 4 224 000.",IF(ABS(C21-(ROUND(3840000*1.1/(360*1.1),0)))&lt;=1,"Du har økt dekningsbidraget per time også. Det er uendret på 360; bare de faste kostnadene stiger.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="19" t="str">
+      <c r="B22" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G22" s="20" t="str">
         <f aca="false">IF(C22="","Skriv svaret i den gule cellen.",IF(ABS(C22-((14400-ROUND(3840000*1.1/360,0))/14400))&lt;=0.003,"Riktig.",IF(ABS(C22-((14400-ROUND(3840000/360,0))/14400))&lt;=0.003,"Det er marginen i dag, 25,9 %. Bruk det nye nullpunktet fra a.","Ikke riktig ennå. Margin i timer = 14 400 − nullpunktet fra a. Delt på 14 400. Cellen er prosentformatert.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="19" t="str">
+      <c r="B23" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="20" t="str">
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(ABS(C23-(ROUND(3840000*0.9/360,0)))&lt;=1,"Riktig.",IF(ABS(C23-(ROUND(3840000/360,0)))&lt;=1,"Det er nullpunktet i dag. Bruk de nye faste kostnadene, 3 456 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="19" t="str">
+      <c r="B24" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="20" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(ABS(C24-(ROUND(3840000/404.5,0)))&lt;=1,"Riktig.",IF(ABS(C24-(ROUND(3840000/(360*1.05),0)))&lt;=1,"Du har økt dekningsbidraget med 5 %. Det er timeprisen som øker 5 %: 44,50 kr, og hele beløpet går inn i dekningsbidraget per time, som blir 404,50.",IF(ABS(C24-(ROUND(3840000/360,0)))&lt;=1,"Det er nullpunktet i dag. Dekningsbidraget per time er nå 360 + 44,50 = 404,50.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" s="19" t="str">
+      <c r="B25" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="20" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(ABS(C25-(ROUND(3840000/315.5,0)))&lt;=1,"Riktig.",IF(ABS(C25-(ROUND(3840000/(360*0.95),0)))&lt;=1,"Du har redusert dekningsbidraget med 5 %. Det er timeprisen som faller 5 %: 44,50 kr, så dekningsbidraget per time blir 315,50.",IF(ABS(C25-(ROUND(3840000/404.5,0)))&lt;=1,"Det er svaret i d, prisen opp. Her går prisen ned: 315,50 kr per time.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" s="19" t="str">
+      <c r="B26" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" s="20" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(10000*360-3840000),"Riktig.",IF(ABS(C26-(10000*360))&lt;=0,"Det er dekningsbidraget ved 10 000 timer. Trekk fra de faste kostnadene, 3 840 000.",IF(ABS(C26-(3840000-10000*360))&lt;=0,"Fortegnet er snudd: Nordlys taper penger ved 10 000 timer, så resultatet er negativt.",IF(ABS(C26-(14400*360-3840000))&lt;=0,"Det er resultatet ved 14 400 timer, 1 344 000. Oppgaven spør om 10 000 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="G28" s="19" t="str">
+      <c r="B28" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="G28" s="20" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Timeprisen opp 5 %","Riktig. 5 % på prisen er 44,50 kr, og hele beløpet går inn i dekningsbidraget per time: 12,4 % mer per time. 10 % på de faste er bare 10 % på de faste. Derfor 9 494 timer mot 9 600. Men prisen er også spaken kunden kan si nei til.","Ikke riktig. 5 % på prisen er 44,50 kr, og hele beløpet går inn i dekningsbidraget per time: 12,4 % mer per time. 10 % på de faste er bare 10 % på de faste. Derfor 9 494 timer mot 9 600. Men prisen er også spaken kunden kan si nei til."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="B30" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="24" t="str">
+      <c r="B34" s="25" t="str">
         <f aca="false">IF(LEN(B31)&lt;40,"",IF(AND(ISNUMBER(SEARCH("pris",B31)),ISNUMBER(SEARCH("faste",B31))),"Bra: du tar stilling til både prisen og de faste kostnadene. Si også at et år med 10 000 timer går med tap uansett, så ordreboka må fylles først.",IF(OR(ISNUMBER(SEARCH("pris",B31)),ISNUMBER(SEARCH("faste",B31))),"Du er på sporet. Ta med både timeprisen (virker mest, men kunden kan si nei) og de faste kostnadene (bilen og kontorplassen kan vente).","Tips: prisen flytter nullpunktet mest, men kunden kan si nei. Bilen og kontorplassen bør vente til timene er der. Og 10 000 timer gir −240 000 kr uansett: det er ordreboka som må fylles.")))</f>
         <v/>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="20"/>
+      <c r="B35" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22" t="str">
+      <c r="B36" s="23" t="str">
         <f aca="false">IF(C35="JA","Hint: a: 4 224 000 / 360 = 11 733,3 → 11 734. b: (14 400 − 11 734) / 14 400 = 18,5 %. c: 3 456 000 / 360 = 9 600. d: 3 840 000 / 404,50 = 9 493,2 → 9 494. e: 3 840 000 / 315,50 = 12 171,2 → 12 172. f: 10 000 × 360 − 3 840 000 = −240 000.","")</f>
         <v/>
       </c>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
+      <c r="B38" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -2318,7 +2364,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Timeprisen opp 5 %,Faste kostnader ned 10 %,De gir samme nullpunkt"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
@@ -2351,243 +2397,243 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="28" t="s">
-        <v>91</v>
+      <c r="B2" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>95</v>
+      <c r="B5" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="26" t="n">
+      <c r="B6" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="27" t="n">
         <v>5184000</v>
       </c>
-      <c r="D6" s="30" t="s">
-        <v>97</v>
+      <c r="D6" s="31" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="30" t="s">
-        <v>99</v>
+      <c r="B7" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="31" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="26" t="n">
+      <c r="B8" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="27" t="n">
         <v>16592593</v>
       </c>
-      <c r="D8" s="30" t="s">
-        <v>101</v>
+      <c r="D8" s="31" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="26" t="n">
+      <c r="B9" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="27" t="n">
         <v>360</v>
       </c>
-      <c r="D9" s="30" t="s">
-        <v>103</v>
+      <c r="D9" s="31" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="26" t="n">
+      <c r="B10" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="27" t="n">
         <v>10667</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>105</v>
+      <c r="D10" s="31" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="30" t="s">
-        <v>107</v>
+      <c r="B11" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="31" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="26" t="n">
+      <c r="B12" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="27" t="n">
         <v>5807407</v>
       </c>
-      <c r="D12" s="30" t="s">
-        <v>109</v>
+      <c r="D12" s="31" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="30" t="s">
-        <v>111</v>
+      <c r="B13" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="27"/>
+      <c r="D13" s="31" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="26" t="n">
+      <c r="B14" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="27" t="n">
         <v>3733</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>113</v>
+      <c r="D14" s="31" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="26" t="n">
+      <c r="B15" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="27" t="n">
         <v>7300</v>
       </c>
-      <c r="D15" s="30" t="s">
-        <v>115</v>
+      <c r="D15" s="31" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="26" t="n">
+      <c r="B16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="27" t="n">
         <v>288</v>
       </c>
-      <c r="D16" s="30" t="s">
-        <v>117</v>
+      <c r="D16" s="31" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="26" t="n">
+      <c r="B17" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="27" t="n">
         <v>-567000</v>
       </c>
-      <c r="D17" s="30" t="s">
-        <v>119</v>
+      <c r="D17" s="31" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="30" t="s">
-        <v>121</v>
+      <c r="B18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="27"/>
+      <c r="D18" s="31" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="26" t="n">
+      <c r="B19" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="27" t="n">
         <v>11734</v>
       </c>
-      <c r="D19" s="30" t="s">
-        <v>123</v>
+      <c r="D19" s="31" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="30" t="s">
-        <v>125</v>
+      <c r="B20" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="31" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="26" t="n">
+      <c r="B21" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="27" t="n">
         <v>9600</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>127</v>
+      <c r="D21" s="31" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="26" t="n">
+      <c r="B22" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="27" t="n">
         <v>9494</v>
       </c>
-      <c r="D22" s="30" t="s">
-        <v>129</v>
+      <c r="D22" s="31" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="26" t="n">
+      <c r="B23" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="27" t="n">
         <v>12172</v>
       </c>
-      <c r="D23" s="30" t="s">
-        <v>131</v>
+      <c r="D23" s="31" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="26" t="n">
+      <c r="B24" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" s="27" t="n">
         <v>-240000</v>
       </c>
-      <c r="D24" s="30" t="s">
-        <v>133</v>
+      <c r="D24" s="31" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="30" t="s">
-        <v>135</v>
+      <c r="B25" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="27"/>
+      <c r="D25" s="31" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="30" t="s">
-        <v>137</v>
+      <c r="B26" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="27"/>
+      <c r="D26" s="31" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok08/OK08_Nullpunktsanalyse_Oppgaver_v6.xlsx
+++ b/pensum/ok08/OK08_Nullpunktsanalyse_Oppgaver_v6.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">1A  Nordlys 2026: nullpunktet i kroner og i timer</t>
   </si>
   <si>
-    <t xml:space="preserve">1B  Sikkerhetsmarginen, og serviceavdelingen som har mye å gjøre</t>
+    <t xml:space="preserve">1B  Sikkerhetsmarginen, og serviceavdelingen som føler at den har mye å gjøre</t>
   </si>
   <si>
     <t xml:space="preserve">1C  Fire tiltak før et stille år: hva skjer med nullpunktet?</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
-    <t xml:space="preserve">Kari Nordlund er daglig leder i Nordlys Elektro. Hun legger budsjettet for 2027, og et nybyggprosjekt kan bli utsatt. Hun spør Ida, som er kalkulatør: hvor mye må vi selge for å gå i null? Regnskapet for 2026 er delt i faste og variable kostnader, slik kapittel 2 gjør det.</t>
+    <t xml:space="preserve">Kari Nordlund er daglig leder i Nordlys Elektro. Banken skal fornye kassekreditten og ber om budsjett for 2027, og et nybyggprosjekt som ikke er kontraktsfestet, kan bli skjøvet til 2028. Kari vil vite hvor mye Nordlys må selge for å gå i null, og ber regnskapsføreren dele regnskapet i faste og variable kostnader. Regnskapet for 2026 er delt i faste og variable kostnader, slik kapittel 2 gjør det.</t>
   </si>
   <si>
     <t xml:space="preserve">Begrepene du trenger</t>
@@ -168,10 +168,10 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppgave 1B: Sikkerhetsmarginen, og serviceavdelingen som har mye å gjøre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Først hele Nordlys: hvor mye kan salget svikte før tapet kommer? Så serviceavdelingen: Tom Berg er driftsleder, og to av montørene hans tar sikringsskapbytter, feilsøking og el-kontroller. Tom har planlagt 210 oppdrag neste år, montørene har mye å gjøre, og han mener avdelingen bærer seg.</t>
+    <t xml:space="preserve">Oppgave 1B: Sikkerhetsmarginen, og serviceavdelingen som føler at den har mye å gjøre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Først hele Nordlys: hvor mye kan salget svikte før tapet kommer? Så serviceavdelingen: Tom Berg er driftsleder, og to av montørene hans tar sikringsskapbytter, feilsøking og el-kontroller. Tom har planlagt 210 oppdrag neste år, synes montørene har mye å gjøre, og mener avdelingen bærer seg. Timene som ikke går til service, lånes ut til prosjektavdelingen.</t>
   </si>
   <si>
     <t xml:space="preserve">Sikkerhetsmargin (boka: risikomargin) = virkelig salg − salget i nullpunktet, i kroner, timer eller prosent av salget. Dekningsbidrag per oppdrag = pris − variable kostnader per oppdrag. Nullpunkt i antall = faste kostnader / dekningsbidrag per enhet, rundet opp. Resultat = dekningsbidrag totalt − faste kostnader.</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">f) Resultat ved 210 oppdrag: dekningsbidrag ved 210 minus faste kostnader (tap med minus)</t>
   </si>
   <si>
-    <t xml:space="preserve">g) Tom sier at serviceavdelingen bærer seg fordi montørene har mye å gjøre. Svar ham i to setninger, med nullpunktet og resultatet ved 210 oppdrag.</t>
+    <t xml:space="preserve">g) Tom sier at serviceavdelingen bærer seg fordi han synes montørene har mye å gjøre. Svar ham i to setninger, med nullpunktet og resultatet ved 210 oppdrag.</t>
   </si>
   <si>
     <t xml:space="preserve">Timeprisen opp 5 %</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">De gir samme nullpunkt</t>
   </si>
   <si>
-    <t xml:space="preserve">Kari tror 2027 blir et stille år og vurderer fire tiltak: en ny servicebil på leasing og én til på kontoret, eller det motsatte: si opp leasingen på en bil og kutte kurs. Og timeprisen: opp 5 % for å tjene mer per time, eller ned 5 % for å vinne flere jobber. Hun endrer én ting om gangen, slik boka gjør det.</t>
+    <t xml:space="preserve">Kari tror 2027 blir et stille år og vurderer fire tiltak: en ny servicebil på leasing og én til på kontoret, eller det motsatte: si opp leasingen på en bil og kutte kurs som ikke er lovpålagt, for eksempel produktkurs hos leverandørene (FSE-kurset og førstehjelp skal holdes minst hver 12. måned etter FSE § 7). Og timeprisen: opp 5 % for å tjene mer per time, eller ned 5 % for å vinne flere jobber. Hun endrer én ting om gangen, slik boka gjør det.</t>
   </si>
   <si>
     <t xml:space="preserve">Nullpunkt i timer = faste kostnader / dekningsbidrag per time. En endring i de faste kostnadene flytter nullpunktet uten å røre dekningsbidraget. En endring i timeprisen går i sin helhet inn i dekningsbidraget per time, for de variable kostnadene er de samme. Resultat = timer × dekningsbidrag per time − faste kostnader.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nordlys i dag: faste kostnader 3 840 000 kr, dekningsbidrag 360 kr per fakturert time, 14 400 fakturerte timer, timepris 890 kr. Nullpunktet er 10 667 timer. Kari vurderer fire tiltak før det hun tror blir et stille år, og hun endrer én ting om gangen, slik boka gjør det i eksempeloppgaven i avsnitt 8.3.</t>
+    <t xml:space="preserve">Nordlys i dag: faste kostnader 3 840 000 kr, dekningsbidrag 360 kr per fakturert time, 14 400 fakturerte timer, timepris 890 kr. Nullpunktet er 10 667 timer. Kari vurderer fire tiltak før det hun tror blir et stille år, og hun endrer én ting om gangen, slik boka gjør det i eksempeloppgaven i avsnitt 8.3. Dekningsbidraget på 360 kr per time bygger på bokas forutsetning om at montørlønna følger timene.</t>
   </si>
   <si>
     <t xml:space="preserve">Tiltak</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">a) Ny servicebil på leasing og én til på kontoret: faste kostnader opp 10 %</t>
   </si>
   <si>
-    <t xml:space="preserve">c) Si opp leasingen på en bil og kutte kurs: faste kostnader ned 10 %</t>
+    <t xml:space="preserve">c) Si opp leasingen på en bil og kutte produktkurs: faste kostnader ned 10 %</t>
   </si>
   <si>
     <t xml:space="preserve">d) Timeprisen opp 5 %: 890 → 934,50 kr</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">e) Nullpunkt i timer når timeprisen går ned 5 % (dekningsbidrag per time 360 − 44,50)</t>
   </si>
   <si>
-    <t xml:space="preserve">f) Resultat i et stille år med 10 000 timer og uendret pris (tap med minus)</t>
+    <t xml:space="preserve">f) Resultat i et stille år med 10 000 timer og uendret pris, med bokas forutsetning om at montørlønna følger timene (tap med minus)</t>
   </si>
   <si>
     <t xml:space="preserve">g) Kari kan velge ett tiltak: timeprisen opp 5 % eller de faste kostnadene ned 10 %. Hvilket gir lavest nullpunkt?</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">1B b) Sikkerhetsmargin i prosent</t>
   </si>
   <si>
-    <t xml:space="preserve">5 807 407 × 100 / 22 400 000 = 25,9 %. Hver fjerde time kan svikte</t>
+    <t xml:space="preserve">5 807 407 × 100 / 22 400 000 = 25,9 % med bokas forutsetning om variabel montørlønn. Med fast montørlønn: nullpunkt 12 980 timer og margin 9,9 %</t>
   </si>
   <si>
     <t xml:space="preserve">1B c) Sikkerhetsmargin i timer</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">1C f) Resultat ved 10 000 timer</t>
   </si>
   <si>
-    <t xml:space="preserve">10 000 × 360 − 3 840 000 = −240 000 kr</t>
+    <t xml:space="preserve">10 000 × 360 − 3 840 000 = −240 000 kr med bokas forutsetning. Med fast montørlønn som løper uansett: 10 000 × 946 − 12 280 000 ≈ −2 820 000 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1C g) Lavest nullpunkt</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">1C h) Rådet til Kari</t>
   </si>
   <si>
-    <t xml:space="preserve">Prisen virker mest, men kunden kan si nei. Bilen og kontorplassen bør vente til timene er der. Et år med 10 000 timer gir −240 000 kr uansett; ordreboka må fylles først</t>
+    <t xml:space="preserve">Ikke sett opp timeprisen fordi året blir stille: prisen regnes av normal aktivitet (kapittel 5), og kunden kan si nei. Bilen og kontorplassen bør vente til timene er der. Et år med 10 000 timer gir −240 000 kr etter boka og om lag −2,8 millioner med fast montørlønn; ordreboka må fylles først</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1189,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>19</v>
       </c>
@@ -1988,7 +1988,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>76</v>
       </c>
@@ -2028,7 +2028,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="9" t="s">
         <v>78</v>
       </c>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C28" s="21"/>
       <c r="G28" s="20" t="str">
-        <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Timeprisen opp 5 %","Riktig. 5 % på prisen er 44,50 kr, og hele beløpet går inn i dekningsbidraget per time: 12,4 % mer per time. 10 % på de faste er bare 10 % på de faste. Derfor 9 494 timer mot 9 600. Men prisen er også spaken kunden kan si nei til.","Ikke riktig. 5 % på prisen er 44,50 kr, og hele beløpet går inn i dekningsbidraget per time: 12,4 % mer per time. 10 % på de faste er bare 10 % på de faste. Derfor 9 494 timer mot 9 600. Men prisen er også spaken kunden kan si nei til."))</f>
+        <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Timeprisen opp 5 %","Riktig. 5 % på prisen er 44,50 kr, og hele beløpet går inn i dekningsbidraget per time: 12,4 % mer per time. 10 % på de faste er bare 10 % på de faste. Derfor 9 494 timer mot 9 600. Men prisen er også spaken kunden kan si nei til, og timeprisen skal regnes av normal aktivitet: et stille år er ingen grunn til å sette den opp (kapittel 5).","Ikke riktig. 5 % på prisen er 44,50 kr, og hele beløpet går inn i dekningsbidraget per time: 12,4 % mer per time. 10 % på de faste er bare 10 % på de faste. Derfor 9 494 timer mot 9 600. Men prisen er også spaken kunden kan si nei til, og timeprisen skal regnes av normal aktivitet: et stille år er ingen grunn til å sette den opp (kapittel 5)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="25" t="str">
-        <f aca="false">IF(LEN(B31)&lt;40,"",IF(AND(ISNUMBER(SEARCH("pris",B31)),ISNUMBER(SEARCH("faste",B31))),"Bra: du tar stilling til både prisen og de faste kostnadene. Si også at et år med 10 000 timer går med tap uansett, så ordreboka må fylles først.",IF(OR(ISNUMBER(SEARCH("pris",B31)),ISNUMBER(SEARCH("faste",B31))),"Du er på sporet. Ta med både timeprisen (virker mest, men kunden kan si nei) og de faste kostnadene (bilen og kontorplassen kan vente).","Tips: prisen flytter nullpunktet mest, men kunden kan si nei. Bilen og kontorplassen bør vente til timene er der. Og 10 000 timer gir −240 000 kr uansett: det er ordreboka som må fylles.")))</f>
+        <f aca="false">IF(LEN(B31)&lt;40,"",IF(AND(ISNUMBER(SEARCH("pris",B31)),ISNUMBER(SEARCH("faste",B31))),"Bra: du tar stilling til både prisen og de faste kostnadene. Si også at et år med 10 000 timer går med tap uansett, så ordreboka må fylles først.",IF(OR(ISNUMBER(SEARCH("pris",B31)),ISNUMBER(SEARCH("faste",B31))),"Du er på sporet. Ta med både timeprisen (virker mest på papiret, men skal ikke settes opp fordi året blir stille) og de faste kostnadene (bilen og kontorplassen kan vente).","Tips: prisen flytter nullpunktet mest, men timeprisen regnes av normal aktivitet, og i et stille år mister du heller oppdrag. Bilen og kontorplassen bør vente til timene er der. Og 10 000 timer gir −240 000 kr med bokas forutsetning, og nær −2,8 millioner når montørene får fast lønn uansett: det er ordreboka som må fylles.")))</f>
         <v/>
       </c>
       <c r="C34" s="25"/>
@@ -2627,7 +2627,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="31" t="s">
         <v>142</v>
       </c>

--- a/pensum/ok08/OK08_Nullpunktsanalyse_Oppgaver_v6.xlsx
+++ b/pensum/ok08/OK08_Nullpunktsanalyse_Oppgaver_v6.xlsx
@@ -652,7 +652,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -779,6 +779,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1066,7 +1070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1091,27 +1095,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1247,16 +1251,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="13" t="n">
         <v>22400000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="13" t="n">
@@ -1269,8 +1273,8 @@
       </c>
       <c r="C14" s="14"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B15" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="13" t="n">
@@ -1375,7 +1379,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
         <v>43</v>
       </c>
@@ -1647,8 +1651,8 @@
         <v>18500</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B19" t="s">
         <v>58</v>
       </c>
       <c r="C19" s="13" t="n">
@@ -1689,7 +1693,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="9" t="s">
         <v>62</v>
       </c>
@@ -2060,8 +2064,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B13" t="s">
         <v>83</v>
       </c>
       <c r="C13" s="27" t="n">
@@ -2072,8 +2076,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B14" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="27" t="n">
@@ -2096,8 +2100,8 @@
         <v>404.5</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="12" t="s">
+    <row ht="31.5" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="32" r="B16" t="s">
         <v>86</v>
       </c>
       <c r="C16" s="13" t="n">
@@ -2193,7 +2197,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="17" t="s">
         <v>94</v>
       </c>
@@ -2206,7 +2210,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
         <v>95</v>
       </c>
